--- a/test/demo-mar-2025/heatingOrCoolingAndPower/fixtures/profiles.xlsx
+++ b/test/demo-mar-2025/heatingOrCoolingAndPower/fixtures/profiles.xlsx
@@ -39,7 +39,7 @@
     <t>Days in the year</t>
   </si>
   <si>
-    <t>Newcastle</t>
+    <t>Southcastle</t>
   </si>
   <si>
     <t>Heating</t>
@@ -81,9 +81,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -91,9 +91,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -122,10 +122,13 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -386,10 +389,10 @@
       <c r="D3" s="7">
         <v>46022.0</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="8">
         <v>70.0</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="8">
         <v>365.0</v>
       </c>
     </row>
@@ -406,10 +409,10 @@
       <c r="D4" s="7">
         <v>46022.0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="8">
         <v>30.0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="8">
         <v>365.0</v>
       </c>
     </row>
@@ -426,7 +429,7 @@
       <c r="D5" s="7">
         <v>46022.0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="8">
         <v>365.0</v>
       </c>
     </row>
@@ -443,38 +446,38 @@
       <c r="D6" s="7">
         <v>46022.0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="8">
         <v>365.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="B8" s="8"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="B9" s="8"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="K9" s="5"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="B10" s="8"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="K10" s="5"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="K11" s="5"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="K12" s="5"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" ht="14.25" customHeight="1"/>
     <row r="14" ht="14.25" customHeight="1"/>
